--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/20 11:34:21</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8536.59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8536.59</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-1463.41</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,210 +75,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/20 11:56:39</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>24096.39</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/20 11:34:05</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>70000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>8536.59</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>xiaoshuai5688</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>时间</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>金额</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>标记人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>操作人</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>32632.97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>-1463.41</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22632.97</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32632.97</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>32632.97</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10888</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>22632.97</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21744.97</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -271,83 +271,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>32632.97</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>32632.97</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11076</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>21744.97</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21556.97</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -298,83 +298,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>32632.97</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>32632.97</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>31076</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21556.97</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1556.97</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -244,12 +244,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/20 12:13:31</t>
+          <t>09/20 12:16:10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>suchen668</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -271,12 +271,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/20 11:57:04</t>
+          <t>09/20 12:13:31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -286,7 +286,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -298,12 +298,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>09/20 11:56:54</t>
+          <t>09/20 11:57:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -325,83 +325,110 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>09/20 11:56:54</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>xiaoshuai5688</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>09/20 11:34:21</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>10000</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>Nikotian01</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>270000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>32632.97</t>
+          <t>270000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>32632.97</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>32076</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1556.97</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>556.97</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -72,186 +72,144 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>09/21 11:54:07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>280000</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>7.95</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>35220.13</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>tiaowu7888</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>35220.13</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>35220.13</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/28 14:39:47</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>260000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>32911.39</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32911.39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>32911.39</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/28 14:39:47</t>
+          <t>09/29 11:25:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>260000</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>32911.39</t>
+          <t>12500</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/29 12:36:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12500</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/29 11:25:52</t>
+          <t>09/30 15:10:45</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>18867.92</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/29 12:36:05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12500</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>18867.92</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12500</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>18867.92</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/30 19:09:56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>150000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>150000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18867.92</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18867</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>18867.92</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.92</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/30 15:10:45</t>
+          <t>10/01 14:48:52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>12658.23</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/30 19:09:56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>18867</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>12658.23</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18867.92</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18867</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.92</t>
+          <t>12658.23</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/01 15:53:56</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12658</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12658.23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12658</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12658.23</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.23</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/01 14:48:52</t>
+          <t>10/06 10:20:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>8.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>12121.21</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xinhui9</t>
+          <t>xiaoshuai5688</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/01 15:53:56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12658</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12658.23</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12658</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.23</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/06 11:58:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12121.21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>12121.21</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.21</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/06 10:20:02</t>
+          <t>10/07 12:39:04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>xiaoshuai5688</t>
+          <t>USDT16889888</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/06 11:58:58</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>37037.04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12121.21</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12121</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.21</t>
+          <t>37037.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/07 13:40:42</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>36987</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nikotian01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37037.04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>36987</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>37037.04</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>50.04</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/07 12:39:04</t>
+          <t>10/14 10:48:20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>28025.48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>USDT16889888</t>
+          <t>Nikotian01</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/07 13:40:42</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>36987</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nikotian01</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>28025.48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>36987</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>50.04</t>
+          <t>28025.48</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/14 10:48:20</t>
+          <t>10/23 10:38:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nikotian01</t>
+          <t>xinhui9</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -215,7 +215,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
@@ -227,7 +227,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
@@ -251,7 +251,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>28025.48</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/23 10:38:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6097.56</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5909.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>10/23 13:23:39</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10/23 10:38:36</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>xinhui9</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1188</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5909.56</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4909.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,7 +75,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/23 10:38:30</t>
+          <t>10/27 10:15:34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/23 13:23:39</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10/23 10:38:36</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>6097.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1188</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4909.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10/27 10:15:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>xinhui9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6097.56</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5909.56</t>
         </is>
       </c>
     </row>

--- a/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
+++ b/bills/huixinjiqiren/-1004438421344/072d10f2aaeb30a9a94c362f5a21017c24c40b1abe4686e59da5edd23291c930/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10/27 10:15:34</t>
+          <t>10/30 09:55:31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>15189.87</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10/27 10:15:38</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>xinhui9</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>120000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>15189.87</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>188</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5909.56</t>
+          <t>15189.87</t>
         </is>
       </c>
     </row>
